--- a/data/trans_orig/IP25B_1_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP25B_1_R-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13001</t>
+          <t>12835</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26736</t>
+          <t>27073</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34124</t>
+          <t>33092</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71856</t>
+          <t>69430</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51429</t>
+          <t>51813</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>96110</t>
+          <t>97386</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>38,19%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87866</t>
+          <t>87529</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101601</t>
+          <t>101767</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68556</t>
+          <t>70982</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>106288</t>
+          <t>107320</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158904</t>
+          <t>157628</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>203585</t>
+          <t>203201</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29199</t>
+          <t>29587</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49138</t>
+          <t>48938</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40634</t>
+          <t>38952</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64331</t>
+          <t>63348</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74324</t>
+          <t>73947</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107808</t>
+          <t>105658</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,84%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>140196</t>
+          <t>140396</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>160135</t>
+          <t>159747</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>189565</t>
+          <t>190548</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>213262</t>
+          <t>214944</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>335422</t>
+          <t>337572</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>368906</t>
+          <t>369283</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,32%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46978</t>
+          <t>46953</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115982</t>
+          <t>118232</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40956</t>
+          <t>41221</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66664</t>
+          <t>67516</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97539</t>
+          <t>96640</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>182166</t>
+          <t>177491</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>48,65%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68165</t>
+          <t>65915</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>137169</t>
+          <t>137194</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>114013</t>
+          <t>113161</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>139721</t>
+          <t>139456</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>182658</t>
+          <t>187333</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>267285</t>
+          <t>268184</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,51%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24116</t>
+          <t>24104</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41043</t>
+          <t>40680</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23839</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42957</t>
+          <t>42819</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52648</t>
+          <t>52575</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>78497</t>
+          <t>77577</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>121869</t>
+          <t>122232</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>138796</t>
+          <t>138808</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>137118</t>
+          <t>137256</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>156236</t>
+          <t>156535</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>264489</t>
+          <t>265409</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>290338</t>
+          <t>290411</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,67%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>132180</t>
+          <t>131679</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>228954</t>
+          <t>231542</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>156383</t>
+          <t>157692</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>214708</t>
+          <t>216130</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>305178</t>
+          <t>306744</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>420889</t>
+          <t>417915</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,72%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>422040</t>
+          <t>419452</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>518814</t>
+          <t>519315</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>540352</t>
+          <t>538930</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>598677</t>
+          <t>597368</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>985166</t>
+          <t>988140</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1100877</t>
+          <t>1099311</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,18%</t>
         </is>
       </c>
     </row>
